--- a/sources/nina_step3.xlsx
+++ b/sources/nina_step3.xlsx
@@ -732,6 +732,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
@@ -804,6 +814,11 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -7394,6 +7409,11 @@
           <t>Special Tag Throw with Anna only. Anna finishes with a Reverse Shoulder Lock. Total damage is 15,30.</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
@@ -7426,6 +7446,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -7463,6 +7488,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -7500,6 +7530,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -7537,6 +7572,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -7574,6 +7614,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -7611,6 +7656,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -7648,6 +7698,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
@@ -7690,6 +7745,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
@@ -7727,6 +7787,11 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
@@ -7764,6 +7829,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
@@ -7806,6 +7876,11 @@
           <t>CH</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
@@ -7838,6 +7913,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
@@ -7875,6 +7955,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>42ce7230-87bf-452a-b714-833a0716e519</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
@@ -7917,6 +8002,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
@@ -7949,6 +8039,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
@@ -7986,6 +8081,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
@@ -8023,6 +8123,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
@@ -8060,6 +8165,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>f956b41d-482e-44be-a215-575d5455d551</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
@@ -8097,6 +8207,11 @@
           <t>Front</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>55a9a5db-779c-4431-878f-621fd1035127</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
@@ -8129,6 +8244,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
@@ -8166,6 +8286,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
@@ -8203,6 +8328,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
@@ -8240,6 +8370,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>55349cf9-9743-4042-9932-3196803d0f29</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
@@ -8277,6 +8412,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
@@ -8312,6 +8452,11 @@
       <c r="K170" t="inlineStr">
         <is>
           <t>1+2</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -8441,6 +8586,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
@@ -8468,6 +8618,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
@@ -8495,6 +8650,11 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
@@ -8522,6 +8682,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
@@ -8549,6 +8714,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
@@ -8576,6 +8746,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
@@ -8603,6 +8778,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
@@ -8630,6 +8810,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
@@ -8657,6 +8842,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
@@ -8684,6 +8874,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>f37af239-8d33-4787-93e6-4352245294b9</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
@@ -8711,6 +8906,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
@@ -8736,6 +8936,11 @@
       <c r="I185" t="inlineStr">
         <is>
           <t>hhhhhllmlm</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
